--- a/DateBase/orders/Nha Thu_2026-5-30.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-30.xlsx
@@ -526,6 +526,9 @@
       <c r="C11" t="str">
         <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -584,7 +587,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0310151578910130</v>
+        <v>03101515789101310</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-30.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-30.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -530,9 +530,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5</v>
+      </c>
+      <c r="C17" t="str">
+        <v>595_玉兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>329_柔丝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>793_珍珠梅粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>792_珍珠梅白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03101515789101310</v>
+        <v>031015157891013105510158105550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-30.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-30.xlsx
@@ -609,6 +609,9 @@
       <c r="C21" t="str">
         <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
       </c>
+      <c r="F21" t="str">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -667,7 +670,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>031015157891013105510158105550</v>
+        <v>031015157891013105510158105552</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-30.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-30.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -610,12 +610,39 @@
         <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
       </c>
       <c r="F21" t="str">
-        <v>2</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>6</v>
+      </c>
+      <c r="C23" t="str">
+        <v>501_姜荷花 绿_Curcuma green_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L24"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -670,7 +697,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>031015157891013105510158105552</v>
+        <v>031015157891013105510158105552022310</v>
       </c>
     </row>
   </sheetData>
